--- a/artfynd/A 47367-2024 artfynd.xlsx
+++ b/artfynd/A 47367-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123321314</v>
       </c>
       <c r="B2" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123321310</v>
       </c>
       <c r="B3" t="n">
-        <v>98402</v>
+        <v>98405</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47367-2024 artfynd.xlsx
+++ b/artfynd/A 47367-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321314</v>
+        <v>123321310</v>
       </c>
       <c r="B2" t="n">
-        <v>97322</v>
+        <v>98407</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598407</v>
+        <v>598289</v>
       </c>
       <c r="R2" t="n">
-        <v>6818587</v>
+        <v>6818707</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_661</t>
+          <t>2024_665</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Intill bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321310</v>
+        <v>123321314</v>
       </c>
       <c r="B3" t="n">
-        <v>98405</v>
+        <v>97324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598289</v>
+        <v>598407</v>
       </c>
       <c r="R3" t="n">
-        <v>6818707</v>
+        <v>6818587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_665</t>
+          <t>2024_661</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>Intill bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 47367-2024 artfynd.xlsx
+++ b/artfynd/A 47367-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123321310</v>
       </c>
       <c r="B2" t="n">
-        <v>98407</v>
+        <v>98413</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123321314</v>
       </c>
       <c r="B3" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47367-2024 artfynd.xlsx
+++ b/artfynd/A 47367-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321314</v>
+        <v>123321310</v>
       </c>
       <c r="B2" t="n">
-        <v>97333</v>
+        <v>98433</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598407</v>
+        <v>598289</v>
       </c>
       <c r="R2" t="n">
-        <v>6818587</v>
+        <v>6818707</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_661</t>
+          <t>2024_665</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Intill bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321310</v>
+        <v>123321314</v>
       </c>
       <c r="B3" t="n">
-        <v>98416</v>
+        <v>97350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598289</v>
+        <v>598407</v>
       </c>
       <c r="R3" t="n">
-        <v>6818707</v>
+        <v>6818587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_665</t>
+          <t>2024_661</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>Intill bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 47367-2024 artfynd.xlsx
+++ b/artfynd/A 47367-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321310</v>
+        <v>123321314</v>
       </c>
       <c r="B2" t="n">
-        <v>98433</v>
+        <v>97367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598289</v>
+        <v>598407</v>
       </c>
       <c r="R2" t="n">
-        <v>6818707</v>
+        <v>6818587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_665</t>
+          <t>2024_661</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>Intill bäck</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321314</v>
+        <v>123321310</v>
       </c>
       <c r="B3" t="n">
-        <v>97350</v>
+        <v>98539</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598407</v>
+        <v>598289</v>
       </c>
       <c r="R3" t="n">
-        <v>6818587</v>
+        <v>6818707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_661</t>
+          <t>2024_665</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Intill bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 47367-2024 artfynd.xlsx
+++ b/artfynd/A 47367-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123321314</v>
       </c>
       <c r="B2" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123321310</v>
       </c>
       <c r="B3" t="n">
-        <v>98539</v>
+        <v>98541</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47367-2024 artfynd.xlsx
+++ b/artfynd/A 47367-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321314</v>
+        <v>123321310</v>
       </c>
       <c r="B2" t="n">
-        <v>97369</v>
+        <v>98116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598407</v>
+        <v>598289</v>
       </c>
       <c r="R2" t="n">
-        <v>6818587</v>
+        <v>6818707</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_661</t>
+          <t>2024_665</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Intill bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321310</v>
+        <v>123321314</v>
       </c>
       <c r="B3" t="n">
-        <v>98541</v>
+        <v>96957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598289</v>
+        <v>598407</v>
       </c>
       <c r="R3" t="n">
-        <v>6818707</v>
+        <v>6818587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_665</t>
+          <t>2024_661</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>Intill bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 47367-2024 artfynd.xlsx
+++ b/artfynd/A 47367-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321310</v>
+        <v>123321314</v>
       </c>
       <c r="B2" t="n">
-        <v>98116</v>
+        <v>96957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598289</v>
+        <v>598407</v>
       </c>
       <c r="R2" t="n">
-        <v>6818707</v>
+        <v>6818587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_665</t>
+          <t>2024_661</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>Intill bäck</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321314</v>
+        <v>123321310</v>
       </c>
       <c r="B3" t="n">
-        <v>96957</v>
+        <v>98116</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598407</v>
+        <v>598289</v>
       </c>
       <c r="R3" t="n">
-        <v>6818587</v>
+        <v>6818707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_661</t>
+          <t>2024_665</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Intill bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 47367-2024 artfynd.xlsx
+++ b/artfynd/A 47367-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321314</v>
+        <v>123321310</v>
       </c>
       <c r="B2" t="n">
-        <v>96957</v>
+        <v>98116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598407</v>
+        <v>598289</v>
       </c>
       <c r="R2" t="n">
-        <v>6818587</v>
+        <v>6818707</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_661</t>
+          <t>2024_665</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Intill bäck</t>
+          <t>I barrskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321310</v>
+        <v>123321314</v>
       </c>
       <c r="B3" t="n">
-        <v>98116</v>
+        <v>96957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,26 +826,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598289</v>
+        <v>598407</v>
       </c>
       <c r="R3" t="n">
-        <v>6818707</v>
+        <v>6818587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_665</t>
+          <t>2024_661</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I barrskog</t>
+          <t>Intill bäck</t>
         </is>
       </c>
       <c r="AD3" t="b">
